--- a/files/港岛-大潭及石澳-皇府湾.xlsx
+++ b/files/港岛-大潭及石澳-皇府湾.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -98,6 +98,22 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="9">
@@ -223,13 +239,13 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -610,7 +626,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-大潭及石澳-皇府湾.xlsx
+++ b/files/港岛-大潭及石澳-皇府湾.xlsx
@@ -626,7 +626,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-大潭及石澳-皇府湾.xlsx
+++ b/files/港岛-大潭及石澳-皇府湾.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -629,6 +629,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -686,6 +690,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -736,6 +760,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -786,6 +830,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -832,6 +896,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -878,6 +962,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -928,6 +1032,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -978,6 +1102,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1028,6 +1172,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1074,6 +1238,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1124,6 +1308,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1174,6 +1378,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1224,6 +1448,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1274,6 +1518,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1324,6 +1588,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1374,6 +1658,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1424,6 +1728,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1474,6 +1798,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1524,6 +1868,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1574,6 +1938,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1624,6 +2008,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1674,6 +2078,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1724,6 +2148,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1770,6 +2214,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1820,6 +2284,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1870,6 +2354,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1920,6 +2424,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1970,6 +2494,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2016,6 +2560,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2066,6 +2630,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2116,6 +2700,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2166,6 +2770,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2216,6 +2840,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2266,6 +2910,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2316,6 +2980,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2366,13 +3050,33 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -2533,7 +3237,7 @@
         <is>
           <t>第3号屋
 2507呎 (4+房)
-(98年-05月)
+(98年-05月-13日)
 $4,706万
 $18,771/呎</t>
         </is>
@@ -2542,7 +3246,7 @@
         <is>
           <t>第5号屋
 2507呎 (4+房)
-(98年-05月)
+(98年-05月-08日)
 $4,600万
 $18,349/呎</t>
         </is>
@@ -2585,7 +3289,7 @@
         <is>
           <t>第9号屋
 2546呎 (4+房)
-(98年-05月)
+(98年-05月-08日)
 $4,880万
 $19,167/呎</t>
         </is>
@@ -2725,7 +3429,7 @@
         <is>
           <t>第25号屋
 3302呎 (4+房)
-(21年-03月)
+(21年-03月-04日)
 $1.25亿
 $37,955/呎</t>
         </is>
@@ -2777,7 +3481,7 @@
         <is>
           <t>第30号屋
 3337呎 (4+房)
-(00年-08月)
+(00年-08月-15日)
 $5,700万
 $17,081/呎</t>
         </is>

--- a/files/港岛-大潭及石澳-皇府湾.xlsx
+++ b/files/港岛-大潭及石澳-皇府湾.xlsx
@@ -3237,7 +3237,7 @@
         <is>
           <t>第3号屋
 2507呎 (4+房)
-(98年-05月-13日)
+(98年-05月)
 $4,706万
 $18,771/呎</t>
         </is>
@@ -3246,7 +3246,7 @@
         <is>
           <t>第5号屋
 2507呎 (4+房)
-(98年-05月-08日)
+(98年-05月)
 $4,600万
 $18,349/呎</t>
         </is>
@@ -3289,7 +3289,7 @@
         <is>
           <t>第9号屋
 2546呎 (4+房)
-(98年-05月-08日)
+(98年-05月)
 $4,880万
 $19,167/呎</t>
         </is>
@@ -3429,7 +3429,7 @@
         <is>
           <t>第25号屋
 3302呎 (4+房)
-(21年-03月-04日)
+(21年-03月)
 $1.25亿
 $37,955/呎</t>
         </is>
@@ -3481,7 +3481,7 @@
         <is>
           <t>第30号屋
 3337呎 (4+房)
-(00年-08月-15日)
+(00年-08月)
 $5,700万
 $17,081/呎</t>
         </is>

--- a/files/港岛-大潭及石澳-皇府湾.xlsx
+++ b/files/港岛-大潭及石澳-皇府湾.xlsx
@@ -3237,7 +3237,7 @@
         <is>
           <t>第3号屋
 2507呎 (4+房)
-(98年-05月)
+(98年-05月-13日)
 $4,706万
 $18,771/呎</t>
         </is>
@@ -3246,7 +3246,7 @@
         <is>
           <t>第5号屋
 2507呎 (4+房)
-(98年-05月)
+(98年-05月-08日)
 $4,600万
 $18,349/呎</t>
         </is>
@@ -3289,7 +3289,7 @@
         <is>
           <t>第9号屋
 2546呎 (4+房)
-(98年-05月)
+(98年-05月-08日)
 $4,880万
 $19,167/呎</t>
         </is>
@@ -3429,7 +3429,7 @@
         <is>
           <t>第25号屋
 3302呎 (4+房)
-(21年-03月)
+(21年-03月-04日)
 $1.25亿
 $37,955/呎</t>
         </is>
@@ -3481,7 +3481,7 @@
         <is>
           <t>第30号屋
 3337呎 (4+房)
-(00年-08月)
+(00年-08月-15日)
 $5,700万
 $17,081/呎</t>
         </is>
